--- a/data/packs/2026-07/ACCOUNT-1008-2026-07.xlsx
+++ b/data/packs/2026-07/ACCOUNT-1008-2026-07.xlsx
@@ -54,10 +54,10 @@
     <t xml:space="preserve">Within first-response commitment</t>
   </si>
   <si>
-    <t xml:space="preserve">Proposals created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deflected</t>
+    <t xml:space="preserve">Suggestions created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-served</t>
   </si>
   <si>
     <t xml:space="preserve">First response attainment</t>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Median, from first_response_minutes_p50</t>
   </si>
   <si>
-    <t xml:space="preserve">Deflection rate</t>
+    <t xml:space="preserve">Self-service rate</t>
   </si>
   <si>
     <t xml:space="preserve">Tickets closed without a person authoring the answer</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Attainment, prior</t>
   </si>
   <si>
-    <t xml:space="preserve">Deflection, prior</t>
+    <t xml:space="preserve">Self-service, prior</t>
   </si>
   <si>
     <t xml:space="preserve">Tickets by product area</t>
